--- a/question_bank/ENGLISH - Transformation of Sentences.xlsx
+++ b/question_bank/ENGLISH - Transformation of Sentences.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="5" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="Voice Change Rules (Treasure)" sheetId="27" r:id="rId6"/>
     <sheet name="Affirmative-Negative" sheetId="10" r:id="rId7"/>
     <sheet name="Transformation (mix)" sheetId="18" r:id="rId8"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Direct - Indirect 1'!$A$1:$B$39</definedName>
@@ -36,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="852">
-  <si>
-    <t>Correct</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="723">
   <si>
     <t>Indirect</t>
   </si>
@@ -519,1886 +515,6 @@
   </si>
   <si>
     <t>Passive</t>
-  </si>
-  <si>
-    <t>She resembles her father.</t>
-  </si>
-  <si>
-    <t>Open the knot.</t>
-  </si>
-  <si>
-    <t>He ate dinner.</t>
-  </si>
-  <si>
-    <t>I sleep in 10am.</t>
-  </si>
-  <si>
-    <t>Both he is poor and greedy</t>
-  </si>
-  <si>
-    <t>You must either do it or I</t>
-  </si>
-  <si>
-    <t>As he was absent, he was marked absent.</t>
-  </si>
-  <si>
-    <t>If I go to Ambala, I shall bring a rattle for you.</t>
-  </si>
-  <si>
-    <t>Neither Payal is here nor Rena.</t>
-  </si>
-  <si>
-    <t>Run fast lest you may be late for school.</t>
-  </si>
-  <si>
-    <t>Though he is poor but he is honest.</t>
-  </si>
-  <si>
-    <t>He no sooner saw the bear but fled away.</t>
-  </si>
-  <si>
-    <t>She had scarcely than her friend arrived.</t>
-  </si>
-  <si>
-    <t>Until you do not speak the truth, I cannot accuse you.</t>
-  </si>
-  <si>
-    <t>She resembles her father. Already correct! "Resembles" does not need a preposition like "with" or "to".</t>
-  </si>
-  <si>
-    <t>He is senior than me.</t>
-  </si>
-  <si>
-    <t>I prefer coffee than tea.</t>
-  </si>
-  <si>
-    <t>She is married with a doctor.</t>
-  </si>
-  <si>
-    <t>Although she worked hard, but she failed the exam.</t>
-  </si>
-  <si>
-    <t>He did not wrote the letter yesterday.</t>
-  </si>
-  <si>
-    <t>The news are true.</t>
-  </si>
-  <si>
-    <t>One of my friends are coming tonight.</t>
-  </si>
-  <si>
-    <t>He has been living here since two years.</t>
-  </si>
-  <si>
-    <t>Look at the birds flying in the sky.</t>
-  </si>
-  <si>
-    <t>I am looking forward to meet you.</t>
-  </si>
-  <si>
-    <t>He behaves as if he knows everything.</t>
-  </si>
-  <si>
-    <t>Scarcely had I entered the room than the lights went out.</t>
-  </si>
-  <si>
-    <t>No sooner did I reach the station when the train left.</t>
-  </si>
-  <si>
-    <t>Unless you do not work hard, you will fail.</t>
-  </si>
-  <si>
-    <t>I, you, and he will study together.</t>
-  </si>
-  <si>
-    <t>The climate of Shimla is better than Delhi.</t>
-  </si>
-  <si>
-    <t>He distributed the sweets between the five children.</t>
-  </si>
-  <si>
-    <t>She is uniqueest girl in the class.</t>
-  </si>
-  <si>
-    <t>He went to the market for buying vegetables.</t>
-  </si>
-  <si>
-    <t>I have seen him last week.</t>
-  </si>
-  <si>
-    <t>Supposing if it rains, what will we do?</t>
-  </si>
-  <si>
-    <t>He coordinates well with his colleagues.</t>
-  </si>
-  <si>
-    <t>Every student must bring their own textbook.</t>
-  </si>
-  <si>
-    <t>Ten miles are a long distance to walk.</t>
-  </si>
-  <si>
-    <t>He died from cancer.</t>
-  </si>
-  <si>
-    <t>The jury were unanimous in its decision.</t>
-  </si>
-  <si>
-    <t>She is more taller than her sister.</t>
-  </si>
-  <si>
-    <t>I am having a large house in the village.</t>
-  </si>
-  <si>
-    <t>He footprinted the thief.</t>
-  </si>
-  <si>
-    <t>The cattle is grazing in the field.</t>
-  </si>
-  <si>
-    <t>Mathematics are a difficult subject for many.</t>
-  </si>
-  <si>
-    <t>He is a honest man.</t>
-  </si>
-  <si>
-    <t>Neither of the two paths lead to the destination.</t>
-  </si>
-  <si>
-    <t>The teacher, along with his students, were present.</t>
-  </si>
-  <si>
-    <t>The reason why he failed is because he didn’t study.</t>
-  </si>
-  <si>
-    <t>He returns back from work at 6 p.m.</t>
-  </si>
-  <si>
-    <t>She is angry on me.</t>
-  </si>
-  <si>
-    <t>I have been waiting here from 9 o'clock.</t>
-  </si>
-  <si>
-    <t>You must compensate the loss.</t>
-  </si>
-  <si>
-    <t>He told to me that he was tired.</t>
-  </si>
-  <si>
-    <t>May I know who are you speaking to?</t>
-  </si>
-  <si>
-    <t>It is me who wrote this poem.</t>
-  </si>
-  <si>
-    <t>What is the price of this dress?</t>
-  </si>
-  <si>
-    <t>The scissor is sharp.</t>
-  </si>
-  <si>
-    <t>She has a great command on English.</t>
-  </si>
-  <si>
-    <t>He is a cousin brother of mine.</t>
-  </si>
-  <si>
-    <t>He ordered for a cup of tea.</t>
-  </si>
-  <si>
-    <t>Can you lend me some money? I am in a great trouble.</t>
-  </si>
-  <si>
-    <t>The presentation was discussed about in the meeting.</t>
-  </si>
-  <si>
-    <t>You must abide by with the rules.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Untie the knot. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Knots are "untied," not "opened."</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He had dinner.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or "He ate his dinner")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>While colloquially used, "had dinner" is more natural in standard English, or "ate" should modify a specific noun.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">He is both poor and greedy. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Both" should immediately precede the two linked adjectives (poor and greedy).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Since he was absent, he was marked absent.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Using "As... he was... he was..." is redundant. "Since" or "Because" works much better here.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>If I go to Ambala, I will bring a rattle for you.</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mostly correct.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In modern English, "will" is preferred over "shall" for simple future intention.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Neither Payal nor Rena is here.Neither... nor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> should directly correlate the two subjects (Payal and Rena).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Though he is poor, he is honest.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or "He is poor but he is honest.")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Though" and "but" are both conjunctions. You only need one to connect the clauses; using both is double-conjunction error.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Unless you speak the truth, I cannot forgive you.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or "Until you speak the truth...")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Until" and "Unless" already carry a negative meaning. Adding "do not" creates an incorrect double negative. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Note: "Accuse" was also likely a typo for a word like "excuse" or "forgive" based on context).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I sleep at 10 a.m. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>We use the preposition at for specific clock times.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Either you must do it, or I must.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or "Either you or I must do it.")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Either... or must connect parallel grammatical structures.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Run fast lest you should be late for school.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The word lest is traditionally followed by the auxiliary verb should (or the subjunctive mood: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"lest you be late"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>No sooner did he see the bear than he fled.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The correlative pair is no sooner... than.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Scarcely had she arrived when her friend arrived.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The correlative pair is scarcely... when (The original sentence was also missing a main verb like </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>arrived</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>left</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the first clause).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He is senior to me. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Words ending in "-ior" like senior, junior, superior take "to", not "than".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I prefer coffee to tea. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Prefer" is always followed by "to".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>She is married to a doctor. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You are married "to" someone.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Although she worked hard, she failed the exam. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Although" and "but" cannot be used together.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He did not write the letter yesterday. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Did" is already past tense; use the base verb "write".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The news is true. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"News" is an uncountable, singular noun.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>One of my friends is coming tonight. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The subject is "One", which is singular.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He has been living here for two years. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use "for" for a duration of time; "since" is for a specific starting point.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Look at the birds flying in the sky. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Correct as written, though sometimes "on the sky" is a common error.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I am looking forward to meeting you. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The phrasal verb "look forward to" requires a gerund/verb+ing.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He behaves as if he knew everything. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"As if" requires the subjunctive past tense for imaginary scenarios.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Scarcely had I entered the room when the lights went out. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Scarcely" pairs with "when".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>No sooner did I reach the station than the train left. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"No sooner" pairs with "than".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Unless you work hard, you will fail. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Unless" already means "if not"; do not add "do not".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>You, he, and I will study together. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>For positive or normal statements, the order of pronouns is 2nd person, 3rd person, 1st person.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The climate of Shimla is better than that of Delhi. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You must compare climate to climate, not climate to a city.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He distributed the sweets among the five children. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Between" is for two people; "among" is for more than two.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>She is the most unique girl in the class. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Or simply "She is a unique girl..." because "unique" is an absolute adjective and cannot be comparative/superlative.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He went to the market to buy vegetables. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use the infinitive "to buy" to express purpose.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I saw him last week. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>With specific past time markers like "last week," use simple past tense, not present perfect.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>If it rains, what will we do? (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Supposing" and "if" mean the same thing; using both is redundant.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He coordinates well with his colleagues. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Correct as written.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Every student must bring his or her own textbook. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Every student" is singular, so it requires a singular pronoun.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ten miles is a long distance to walk. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quantities of distance, time, or money are treated as a single unit and take a singular verb.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He died of cancer. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You die "of" a disease, not "from" it.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The jury was unanimous in its decision. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>When a collective noun acts as a unified whole, it takes a singular verb.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>She is taller than her sister. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"More taller" is a double comparative error.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I have a large house in the village. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Stative/possession verbs like "have" are generally not used in the continuous "-ing" form.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He tracked the footprints of the thief. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Footprinted" is not a standard verb contextually here.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The cattle are grazing in the field. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Cattle" is a plural noun and takes a plural verb.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mathematics is a difficult subject for many. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Subjects ending in "-ics" are singular.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He is an honest man. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The "h" is silent, so it takes the article "an".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Neither of the two paths leads to the destination. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Neither" is singular.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The teacher, along with his students, was present. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phrases like "along with" do not change the number of the singular subject "The teacher".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The reason why he failed is that he didn’t study. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"The reason why... is because" is redundant. Use "is that".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He returns from work at 6 p.m. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Return" means to come back; "returns back" is redundant.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>She is angry with me. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You get angry "with" a person, but angry "at" a situation.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I have been waiting here since 9 o'clock. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use "since" for a specific point in time.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>You must compensate for the loss. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The verb requires the preposition "for".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He told me that he was tired. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Told" takes a direct object; "said to me" or "told me".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>May I know whom you are speaking to? (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use "whom" as it is the object of the preposition.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>It is I who wrote this poem. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use the subject pronoun "I" after forms of the verb "to be" like "is".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">How much does this dress cost? </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or "What is the price of this dress?")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The original is actually acceptable in modern English, but "How much does it cost?" is more natural.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The scissors are sharp. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Scissors" is a plural noun.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>She has a great command of English. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You have a command "of" a language.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He is a cousin of mine. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Never say "cousin brother" or "cousin sister"—just use "cousin".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>He ordered a cup of tea. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Order" is a transitive verb here and does not need "for".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Can you lend me some money? I am in great trouble. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Trouble" is uncountable, so omit "a".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The presentation was discussed in the meeting. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Discussed about" is redundant; "discuss" means to talk about.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>You must abide by the rules. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The phrase is "abide by", not "abide by with".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>Answers</t>
@@ -4106,9 +2222,6 @@
     <t>Do as directed</t>
   </si>
   <si>
-    <t>Correct the following sentences</t>
-  </si>
-  <si>
     <t xml:space="preserve">By way of using negative word with opposite adjectives, an affirmative sentence could be transformed into negative sentence. </t>
   </si>
   <si>
@@ -4287,6 +2400,9 @@
   </si>
   <si>
     <t>Man is not immortal.</t>
+  </si>
+  <si>
+    <t>Syllabus</t>
   </si>
 </sst>
 </file>
@@ -4426,7 +2542,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4435,12 +2551,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4505,8 +2615,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4801,140 +2909,226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:A27"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="139.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="B11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="B12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="B13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="B14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="B18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="B22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="B23">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="B24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="B25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>519</v>
+        <v>390</v>
+      </c>
+      <c r="B27">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -4956,322 +3150,322 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>789</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B2" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B37" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B38" s="11" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B39" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="13"/>
+      <c r="B81" s="11"/>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="13"/>
+      <c r="B82" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B39"/>
@@ -5293,178 +3487,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>789</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
+      <c r="A1" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>467</v>
+      <c r="A2" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>468</v>
+      <c r="A3" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>469</v>
+      <c r="A4" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>470</v>
+      <c r="A5" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>471</v>
+      <c r="A6" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>472</v>
+      <c r="A7" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>473</v>
+      <c r="A8" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>474</v>
+      <c r="A9" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>475</v>
+      <c r="A10" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>476</v>
+      <c r="A11" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>477</v>
+      <c r="A12" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>478</v>
+      <c r="A13" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>479</v>
+      <c r="A14" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>480</v>
+      <c r="A15" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>481</v>
+      <c r="A16" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>482</v>
+      <c r="A17" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>483</v>
+      <c r="A18" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>484</v>
+      <c r="A19" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>485</v>
+      <c r="A20" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>486</v>
+      <c r="A21" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="13"/>
+      <c r="B63" s="11"/>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="13"/>
+      <c r="B64" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B21"/>
@@ -5480,345 +3674,345 @@
   <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="50.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>789</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
+      <c r="A1" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B16" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B28" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B30" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B32" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B33" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B34" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B35" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B38" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B39" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B41" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B42" s="15" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5840,1034 +4034,1034 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>745</v>
+      <c r="A1" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="B2" s="25"/>
+        <v>471</v>
+      </c>
+      <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>520</v>
+        <v>391</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>521</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>523</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>524</v>
+        <v>395</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>525</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>526</v>
+        <v>397</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>527</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>528</v>
+        <v>399</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>529</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>530</v>
+        <v>401</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>531</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>539</v>
+        <v>410</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>532</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>538</v>
+        <v>404</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>534</v>
+        <v>405</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>535</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>536</v>
+        <v>407</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>537</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>601</v>
-      </c>
-      <c r="B14" s="29"/>
+      <c r="A13" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="B14" s="27"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>543</v>
+        <v>414</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>546</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>544</v>
+        <v>415</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>547</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>545</v>
+        <v>416</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>548</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>549</v>
+        <v>420</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>552</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>550</v>
+        <v>421</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>551</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>553</v>
+        <v>424</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>554</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>555</v>
+        <v>426</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>557</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>556</v>
+        <v>427</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>558</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>559</v>
+        <v>430</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>542</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>560</v>
+        <v>431</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>561</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="27" t="s">
-        <v>562</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>563</v>
+      <c r="A25" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>602</v>
-      </c>
-      <c r="B26" s="25"/>
+      <c r="A26" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="B26" s="23"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>564</v>
+        <v>435</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>565</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>566</v>
+        <v>437</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>567</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>568</v>
+        <v>439</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>569</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>570</v>
+        <v>441</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>571</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>572</v>
+        <v>443</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>573</v>
+        <v>444</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>574</v>
+        <v>445</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>575</v>
+        <v>446</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>576</v>
+        <v>447</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>577</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>578</v>
+        <v>449</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>579</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="27" t="s">
-        <v>580</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>581</v>
+      <c r="A35" s="25" t="s">
+        <v>451</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
-        <v>603</v>
-      </c>
-      <c r="B36" s="25"/>
+      <c r="A36" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="B36" s="23"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>587</v>
+        <v>458</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>582</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>583</v>
+        <v>454</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>584</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>585</v>
+        <v>456</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>586</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>588</v>
+        <v>459</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>589</v>
+        <v>460</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>590</v>
+        <v>461</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>591</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>592</v>
+        <v>463</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>593</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>594</v>
+        <v>465</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>597</v>
+        <v>468</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>596</v>
+        <v>466</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
-        <v>598</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>599</v>
+      <c r="A45" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="46" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
-        <v>604</v>
-      </c>
-      <c r="B46" s="30"/>
+      <c r="A46" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="B46" s="28"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>605</v>
+        <v>476</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>606</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>607</v>
+        <v>478</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>608</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>609</v>
+        <v>480</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>610</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>611</v>
+        <v>482</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>612</v>
+        <v>483</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>613</v>
+        <v>484</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>614</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>615</v>
+        <v>486</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>616</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>617</v>
+        <v>488</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>618</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>620</v>
+        <v>491</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>619</v>
+        <v>490</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="27" t="s">
-        <v>621</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>622</v>
+      <c r="A55" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
-        <v>623</v>
-      </c>
-      <c r="B56" s="30"/>
+      <c r="A56" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="B56" s="28"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>625</v>
+        <v>496</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>624</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>626</v>
+        <v>497</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>627</v>
+        <v>498</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>628</v>
+        <v>499</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>629</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>630</v>
+        <v>501</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>631</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="27" t="s">
-        <v>633</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>632</v>
+      <c r="A61" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="B62" s="30"/>
+      <c r="A62" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="B62" s="28"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>636</v>
+        <v>507</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>637</v>
+        <v>508</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>638</v>
+        <v>509</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>639</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>642</v>
+        <v>513</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>643</v>
+        <v>514</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>652</v>
+        <v>523</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>644</v>
+        <v>515</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>650</v>
+        <v>521</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>651</v>
+        <v>522</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>635</v>
+        <v>506</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>645</v>
+        <v>516</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>647</v>
+        <v>518</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>646</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
-        <v>648</v>
-      </c>
-      <c r="B71" s="28" t="s">
-        <v>649</v>
+      <c r="A71" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="B72" s="30"/>
+      <c r="A72" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="B72" s="28"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="B73" s="31" t="s">
-        <v>654</v>
+        <v>526</v>
+      </c>
+      <c r="B73" s="29" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>656</v>
+        <v>527</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>657</v>
+        <v>528</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>658</v>
+        <v>529</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>659</v>
+        <v>530</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>663</v>
+        <v>534</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>660</v>
+        <v>531</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="27" t="s">
-        <v>661</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>662</v>
+      <c r="A77" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="30" t="s">
-        <v>687</v>
-      </c>
-      <c r="B78" s="30"/>
+      <c r="A78" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="B78" s="28"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>692</v>
+        <v>563</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>693</v>
+        <v>564</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>694</v>
+        <v>565</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>695</v>
+        <v>566</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>696</v>
+        <v>567</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>697</v>
+        <v>568</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>698</v>
+        <v>569</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>699</v>
+        <v>570</v>
       </c>
     </row>
     <row r="83" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
-        <v>688</v>
-      </c>
-      <c r="B83" s="30"/>
+      <c r="A83" s="28" t="s">
+        <v>559</v>
+      </c>
+      <c r="B83" s="28"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>700</v>
+        <v>571</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>701</v>
+        <v>572</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>702</v>
+        <v>573</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>703</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>704</v>
+        <v>575</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>705</v>
+        <v>576</v>
       </c>
     </row>
     <row r="87" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="30" t="s">
-        <v>689</v>
-      </c>
-      <c r="B87" s="30"/>
+      <c r="A87" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="B87" s="28"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>706</v>
+        <v>577</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>707</v>
+        <v>578</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>708</v>
+        <v>579</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>709</v>
+        <v>580</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>710</v>
+        <v>581</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>711</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="30" t="s">
-        <v>690</v>
-      </c>
-      <c r="B91" s="30" t="s">
-        <v>690</v>
+      <c r="A91" s="28" t="s">
+        <v>561</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>714</v>
+        <v>585</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>715</v>
+        <v>586</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>712</v>
+        <v>583</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>713</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>716</v>
+        <v>587</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>717</v>
+        <v>588</v>
       </c>
     </row>
     <row r="95" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="30" t="s">
-        <v>691</v>
-      </c>
-      <c r="B95" s="30"/>
+      <c r="A95" s="28" t="s">
+        <v>562</v>
+      </c>
+      <c r="B95" s="28"/>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>719</v>
+        <v>590</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>718</v>
+        <v>589</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="27" t="s">
-        <v>720</v>
-      </c>
-      <c r="B97" s="27" t="s">
-        <v>721</v>
+      <c r="A97" s="25" t="s">
+        <v>591</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="33"/>
-      <c r="B98" s="33"/>
+      <c r="A98" s="31"/>
+      <c r="B98" s="31"/>
     </row>
     <row r="99" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="30" t="s">
-        <v>722</v>
-      </c>
-      <c r="B99" s="30"/>
+      <c r="A99" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="B99" s="28"/>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>723</v>
+        <v>594</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>724</v>
+        <v>595</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>725</v>
+        <v>596</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>726</v>
+        <v>597</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>727</v>
+        <v>598</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>728</v>
+        <v>599</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>729</v>
+        <v>600</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>730</v>
+        <v>601</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>732</v>
+        <v>603</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>731</v>
+        <v>602</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="B105" s="31" t="s">
-        <v>734</v>
+        <v>604</v>
+      </c>
+      <c r="B105" s="29" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>735</v>
+        <v>606</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>736</v>
+        <v>607</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>737</v>
+        <v>608</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>738</v>
+        <v>609</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="B108" s="31" t="s">
-        <v>740</v>
+        <v>610</v>
+      </c>
+      <c r="B108" s="29" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>741</v>
+        <v>612</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>742</v>
+        <v>613</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>744</v>
+        <v>615</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>743</v>
+        <v>614</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>747</v>
+        <v>618</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>748</v>
+        <v>619</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>749</v>
+        <v>620</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>752</v>
+        <v>623</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>750</v>
+        <v>621</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>751</v>
+        <v>622</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
-        <v>746</v>
+      <c r="A115" s="24" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>753</v>
+        <v>624</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>754</v>
+        <v>625</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>755</v>
+        <v>626</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>756</v>
+        <v>627</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>757</v>
+        <v>628</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>758</v>
+        <v>629</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>759</v>
+        <v>630</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>760</v>
+        <v>631</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>761</v>
+        <v>632</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>762</v>
+        <v>633</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>763</v>
+        <v>634</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>764</v>
+        <v>635</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>765</v>
+        <v>636</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>766</v>
+        <v>637</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>767</v>
+        <v>638</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>768</v>
+        <v>639</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>769</v>
+        <v>640</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="B126" s="26"/>
-    </row>
-    <row r="127" spans="1:2" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="B127" s="26"/>
-    </row>
-    <row r="128" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="26" t="s">
-        <v>773</v>
-      </c>
-      <c r="B128" s="26"/>
-    </row>
-    <row r="129" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="26" t="s">
-        <v>774</v>
-      </c>
-      <c r="B129" s="26"/>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="24" t="s">
+        <v>642</v>
+      </c>
+      <c r="B126" s="24"/>
+    </row>
+    <row r="127" spans="1:2" s="22" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="24" t="s">
+        <v>643</v>
+      </c>
+      <c r="B127" s="24"/>
+    </row>
+    <row r="128" spans="1:2" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="24" t="s">
+        <v>644</v>
+      </c>
+      <c r="B128" s="24"/>
+    </row>
+    <row r="129" spans="1:2" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="24" t="s">
+        <v>645</v>
+      </c>
+      <c r="B129" s="24"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>775</v>
+        <v>646</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>776</v>
+        <v>647</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>777</v>
+        <v>648</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>778</v>
+        <v>649</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>779</v>
+        <v>650</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>780</v>
+        <v>651</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>781</v>
+        <v>652</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>782</v>
+        <v>653</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>783</v>
+        <v>654</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>784</v>
+        <v>655</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>785</v>
+        <v>656</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>786</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>787</v>
+        <v>658</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>788</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -6884,113 +5078,113 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.28515625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="55.28515625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>664</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>677</v>
+    <row r="1" spans="1:2" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>665</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>679</v>
+        <v>536</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>680</v>
+        <v>537</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>667</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>686</v>
+        <v>538</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>678</v>
+        <v>545</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>668</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>681</v>
+        <v>539</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>669</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>682</v>
+        <v>540</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>670</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>683</v>
+        <v>541</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>675</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>678</v>
+        <v>546</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>671</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>684</v>
+        <v>542</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>678</v>
+        <v>543</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>673</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>685</v>
+        <v>544</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>676</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>678</v>
+        <v>547</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -7003,264 +5197,264 @@
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.140625" style="36" customWidth="1"/>
+    <col min="1" max="1" width="73.140625" style="32" customWidth="1"/>
     <col min="2" max="2" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>793</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>289</v>
+    <row r="1" spans="1:2" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>663</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>792</v>
+      <c r="A2" s="33" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>837</v>
+      <c r="A3" s="36" t="s">
+        <v>707</v>
       </c>
       <c r="B3" t="s">
-        <v>851</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>838</v>
+      <c r="A4" s="36" t="s">
+        <v>708</v>
       </c>
       <c r="B4" t="s">
-        <v>845</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>839</v>
+      <c r="A5" s="36" t="s">
+        <v>709</v>
       </c>
       <c r="B5" t="s">
-        <v>846</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>840</v>
+      <c r="A6" s="36" t="s">
+        <v>710</v>
       </c>
       <c r="B6" t="s">
-        <v>823</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>841</v>
+      <c r="A7" s="36" t="s">
+        <v>711</v>
       </c>
       <c r="B7" t="s">
-        <v>847</v>
+        <v>717</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>794</v>
+      <c r="A9" s="33" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>842</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>848</v>
+      <c r="A10" s="36" t="s">
+        <v>712</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>843</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>849</v>
+      <c r="A11" s="36" t="s">
+        <v>713</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>844</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>850</v>
+      <c r="A12" s="36" t="s">
+        <v>714</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
-        <v>795</v>
+      <c r="A14" s="33" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
-        <v>796</v>
+      <c r="A15" s="33" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>797</v>
+      <c r="A16" s="32" t="s">
+        <v>667</v>
       </c>
       <c r="B16" t="s">
-        <v>798</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>799</v>
+      <c r="A19" s="33" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>800</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>801</v>
+      <c r="A20" s="32" t="s">
+        <v>670</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>802</v>
+      <c r="A23" s="33" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
-        <v>803</v>
+      <c r="A24" s="32" t="s">
+        <v>673</v>
       </c>
       <c r="B24" t="s">
-        <v>804</v>
+        <v>674</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
-        <v>805</v>
+      <c r="A27" s="33" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>807</v>
+      <c r="A28" s="32" t="s">
+        <v>677</v>
       </c>
       <c r="B28" t="s">
-        <v>806</v>
+        <v>676</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
-        <v>836</v>
+      <c r="A31" s="33" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
-        <v>808</v>
+      <c r="A32" s="32" t="s">
+        <v>678</v>
       </c>
       <c r="B32" t="s">
-        <v>809</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
-        <v>810</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>811</v>
+      <c r="A33" s="32" t="s">
+        <v>680</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>812</v>
+      <c r="A34" s="32" t="s">
+        <v>682</v>
       </c>
       <c r="B34" t="s">
-        <v>813</v>
+        <v>683</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
-        <v>815</v>
+      <c r="A35" s="32" t="s">
+        <v>685</v>
       </c>
       <c r="B35" t="s">
-        <v>814</v>
+        <v>684</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
-        <v>816</v>
+      <c r="A36" s="32" t="s">
+        <v>686</v>
       </c>
       <c r="B36" t="s">
-        <v>817</v>
+        <v>687</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="36" t="s">
-        <v>818</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>823</v>
+      <c r="A37" s="32" t="s">
+        <v>688</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
-        <v>819</v>
+      <c r="A38" s="32" t="s">
+        <v>689</v>
       </c>
       <c r="B38" t="s">
-        <v>820</v>
+        <v>690</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>821</v>
+      <c r="A39" s="32" t="s">
+        <v>691</v>
       </c>
       <c r="B39" t="s">
-        <v>822</v>
+        <v>692</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="36" t="s">
-        <v>824</v>
+      <c r="A40" s="32" t="s">
+        <v>694</v>
       </c>
       <c r="B40" t="s">
-        <v>825</v>
+        <v>695</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="36" t="s">
-        <v>826</v>
+      <c r="A41" s="32" t="s">
+        <v>696</v>
       </c>
       <c r="B41" t="s">
-        <v>827</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
-        <v>829</v>
+      <c r="A42" s="32" t="s">
+        <v>699</v>
       </c>
       <c r="B42" t="s">
-        <v>828</v>
+        <v>698</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
-        <v>831</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>830</v>
+      <c r="A43" s="32" t="s">
+        <v>701</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
-        <v>832</v>
+      <c r="A44" s="32" t="s">
+        <v>702</v>
       </c>
       <c r="B44" t="s">
-        <v>833</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
-        <v>834</v>
+      <c r="A45" s="32" t="s">
+        <v>704</v>
       </c>
       <c r="B45" t="s">
-        <v>835</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -7273,673 +5467,673 @@
   <dimension ref="A1:B83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="89.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="89.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>790</v>
+      <c r="A1" s="7" t="s">
+        <v>661</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="18" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="B3" s="20" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" s="18" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B81" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B82" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="B40" s="20" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B83" s="17" t="s">
         <v>317</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="B64" s="22" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B65" s="22" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="B67" s="22" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B71" s="20" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="B77" s="20" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="B80" s="20" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7948,541 +6142,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="50.7109375" style="33" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="35"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Syllabus!R1C1" display="Correct the following sentences"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>